--- a/tanoshimi/docs/02_요구사항정의서.xlsx
+++ b/tanoshimi/docs/02_요구사항정의서.xlsx
@@ -192,7 +192,7 @@
     <t>로그인</t>
   </si>
   <si>
-    <t>Spring Security Form Login. **username 파라미터명 = email**, 비밀번호 password. 성공 시 /, 실패 시 /login?error=...</t>
+    <t>Spring Security Form Login. username 파라미터명 = email, 비밀번호 password. 성공 시 /, 실패 시 /login?error=...</t>
   </si>
   <si>
     <t>S-02</t>
@@ -587,7 +587,7 @@
     <t>동행 챗봇(Tami)</t>
   </si>
   <si>
-    <t>POST /api/companion/chat (로그인 필요, 사용자별 1분 10회·하루 200회 제한 - app.companion.rate-limit.*. 2026-10-05 보안 수정 전엔 비로그인 무제한이라 AI 요금 소진 위험). 여행 스타일·동행 유형·지역 기반 대화형 추천. mock 프로바이더로 동작 확인. 실 Gemini 실패 시 원본 에러 대신 안내 문구(fix/ai-fallback, #47), 추천은 입력 키워드를 DB 관광지와 매칭하는 폴백(#78). **2026-09-28: 마스코트 위젯은 계획표(/planner/{id}) 화면에서만 노출** — 다른 화면에선 역할이 불분명하고 버튼을 가려 제거</t>
+    <t>POST /api/companion/chat (로그인 필요, 사용자별 1분 10회·하루 200회 제한 - app.companion.rate-limit.*. 2026-10-05 보안 수정 전엔 비로그인 무제한이라 AI 요금 소진 위험). 여행 스타일·동행 유형·지역 기반 대화형 추천. mock 프로바이더로 동작 확인. 실 Gemini 실패 시 원본 에러 대신 안내 문구(fix/ai-fallback, #47), 추천은 입력 키워드를 DB 관광지와 매칭하는 폴백(#78). 2026-09-28: 마스코트 위젯은 계획표(/planner/{id}) 화면에서만 노출 — 다른 화면에선 역할이 불분명하고 버튼을 가려 제거</t>
   </si>
   <si>
     <t>S-15, G-01</t>
